--- a/site/iCIMS-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/iCIMS-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>h_01M4G60864YSQDE01B3ED0HZ6Z</t>
+          <t>h_01M51KAN8WQSR3X6KT5ZZSFP1S</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M4G60864YSQDE01B3ED0HZ6Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51KAN8WQSR3X6KT5ZZSFP1S</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01M4G62PNHPFJTG5T1B81YRVPK</t>
+          <t>h_01M51M85JWHCY7F0K3HKCBGH8A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M4G62PNHPFJTG5T1B81YRVPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51M85JWHCY7F0K3HKCBGH8A</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01M4G63D3HA80RN63N2C766H60</t>
+          <t>h_01M51PD38C4KP8WRZG98QJ6RYY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M4G63D3HA80RN63N2C766H60</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51PD38C4KP8WRZG98QJ6RYY</t>
         </is>
       </c>
     </row>
@@ -517,19 +517,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01M4G63HMVNSSY7ZBNDY1XXQM4</t>
+          <t>h_01M51PM7KMQ10T2S811EQE568F</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M4G63HMVNSSY7ZBNDY1XXQM4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51PM7KMQ10T2S811EQE568F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Create integration</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,12 +539,518 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01M4G64123WYQCQWVC88XV87KJ</t>
+          <t>h_01M51PQ95P4N468XXEGG81KG97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M4G64123WYQCQWVC88XV87KJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51PQ95P4N468XXEGG81KG97</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01M51PRR8FS8FR5P2NA3EPPYQ2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51PRR8FS8FR5P2NA3EPPYQ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Connections</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01M51PY4JGFB2H7EVHM8KJFBQG</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51PY4JGFB2H7EVHM8KJFBQG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01M51PZ9WE0B2KTF2KAVE6S4RD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51PZ9WE0B2KTF2KAVE6S4RD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Event Control Settings</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01M51Q2BWES5F629CW9B2Z4JNZ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51Q2BWES5F629CW9B2Z4JNZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Operational settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01M48R05FPT8VKY52WQXCVB9KM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M48R05FPT8VKY52WQXCVB9KM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Manual candidate execution</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01M51Z2VAVS6GWDJ64457ZCJ7H</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51Z2VAVS6GWDJ64457ZCJ7H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>iCIMS Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01M51Z6X8HPF3Z7RY0YGCH1CJ3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M51Z6X8HPF3Z7RY0YGCH1CJ3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>iCIMS to UKG Ready</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01M5VV17MHCN8XW34T7Y41AZWC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VV17MHCN8XW34T7Y41AZWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UKG Ready Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01M520JXF34PN1YBYY2C528P5N</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M520JXF34PN1YBYY2C528P5N</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Create settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01M5VQY0233QG2Q929NT1QKR75</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VQY0233QG2Q929NT1QKR75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Update settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01M5VJ2TAMW8B0P0DDH75PGT6T</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VJ2TAMW8B0P0DDH75PGT6T</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Delete settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01M5VKRN54HKP0BVX0MCAYBC3W</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VKRN54HKP0BVX0MCAYBC3W</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Employee Data Management</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01M5VM94PZAYNYJWJ99V2JJYDN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VM94PZAYNYJWJ99V2JJYDN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Operation settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01M5VQT7RMBFBCA7TJWWV1QZXT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VQT7RMBFBCA7TJWWV1QZXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01M5VQVQTX9H3Y24BCGE6QVAFX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VQVQTX9H3Y24BCGE6QVAFX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01M5VQWNW69DG3GZM9VC6EBKN5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VQWNW69DG3GZM9VC6EBKN5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01M5VQX84Z6T9VM5V4FAHGVFAD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VQX84Z6T9VM5V4FAHGVFAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01M5VTFZHA603YAFNKD9M5KEGR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VTFZHA603YAFNKD9M5KEGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Notification recipients</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01M5VTG7B577N5J3WM9ZA104RQ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VTG7B577N5J3WM9ZA104RQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execution success notification</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01M5VTHJKRVK9M4K5P4EP65HQF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VTHJKRVK9M4K5P4EP65HQF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Execution failure notification</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01M5VTJEM5YZ28CQ5DJW7V7HMV</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VTJEM5YZ28CQ5DJW7V7HMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Notification report settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01M5VTK8CHQQHZ6AVPSMPJ4Q2H</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VTK8CHQQHZ6AVPSMPJ4Q2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Attribute Mapper</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01M5VTMMHZAFC8G7Y9ATR6MBGH</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-UKG-Ready-Integration-Guide/#h_01M5VTMMHZAFC8G7Y9ATR6MBGH</t>
         </is>
       </c>
     </row>
